--- a/매출건수_업로드_템플릿.xlsx
+++ b/매출건수_업로드_템플릿.xlsx
@@ -1,71 +1,140 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FURSYS\Desktop\sidiz-portal\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="9330"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="매출건수" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="매출건수" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+  <si>
+    <t>월별 매출건수 업로드 템플릿</t>
+  </si>
+  <si>
+    <t>※ year_month 형식: YYYY-MM (예: 2026-03)</t>
+  </si>
+  <si>
+    <t>※ country: 국내 또는 베트남</t>
+  </si>
+  <si>
+    <t>연월</t>
+  </si>
+  <si>
+    <t>국가</t>
+  </si>
+  <si>
+    <t>매출건수</t>
+  </si>
+  <si>
+    <t>매출액(원)</t>
+  </si>
+  <si>
+    <t>year_month</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>sales_count</t>
+  </si>
+  <si>
+    <t>sales_amount</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>국내</t>
+  </si>
+  <si>
+    <t>베트남</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
-    <font>
-      <name val="Calibri"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="8" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00FF0000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,107 +147,57 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -466,194 +485,145 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>월별 매출건수 업로드 템플릿</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>※ year_month 형식: YYYY-MM (예: 2026-03)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>※ country: 국내 또는 베트남</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>연월</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>국가</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>매출건수</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>매출액(원)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>year_month</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>sales_count</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>sales_amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>국내</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6">
         <v>20726</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>베트남</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="6">
         <v>16124</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>국내</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="6">
         <v>21632</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>베트남</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="6">
         <v>17593</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>국내</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D10" s="7">
         <v>0</v>
       </c>
-      <c r="D10" s="7" t="n">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="7">
+        <v>21000</v>
+      </c>
+      <c r="D11" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>베트남</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/매출건수_업로드_템플릿.xlsx
+++ b/매출건수_업로드_템플릿.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>월별 매출건수 업로드 템플릿</t>
   </si>
@@ -67,12 +67,19 @@
   </si>
   <si>
     <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy/mm"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -165,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -182,6 +189,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -486,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -539,7 +552,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -553,7 +566,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -567,7 +580,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -581,7 +594,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -595,32 +608,72 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="7">
-        <v>20000</v>
+      <c r="C10" s="6">
+        <v>10000</v>
       </c>
       <c r="D10" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="7">
-        <v>21000</v>
+      <c r="C11" s="6">
+        <v>8000</v>
       </c>
       <c r="D11" s="7">
         <v>0</v>
       </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>46143</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>46143</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/매출건수_업로드_템플릿.xlsx
+++ b/매출건수_업로드_템플릿.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FURSYS\Desktop\sidiz-portal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FURSYS\Desktop\클로드\sidiz-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -615,7 +615,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="6">
-        <v>10000</v>
+        <v>21457</v>
       </c>
       <c r="D10" s="7">
         <v>0</v>
@@ -629,7 +629,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="6">
-        <v>8000</v>
+        <v>13264</v>
       </c>
       <c r="D11" s="7">
         <v>0</v>
